--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Поплаухина - бухгалтер/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Поплаухина - бухгалтер/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92574202366</v>
+        <v>46157.93116785773</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Поплаухина - бухгалтер/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Поплаухина - бухгалтер/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93116785773</v>
+        <v>46157.93183040842</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Поплаухина - бухгалтер/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Поплаухина - бухгалтер/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93183040842</v>
+        <v>46157.93405485852</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Поплаухина - бухгалтер/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Поплаухина - бухгалтер/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93405485852</v>
+        <v>46157.9372356799</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Поплаухина - бухгалтер/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Поплаухина - бухгалтер/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9372356799</v>
+        <v>46158.28221355015</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Поплаухина - бухгалтер/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Поплаухина - бухгалтер/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28221355015</v>
+        <v>46158.29701610491</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Поплаухина - бухгалтер/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Поплаухина - бухгалтер/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29701610491</v>
+        <v>46158.2982106873</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Поплаухина - бухгалтер/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Поплаухина - бухгалтер/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.2982106873</v>
+        <v>46158.33392406986</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Поплаухина - бухгалтер/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Поплаухина - бухгалтер/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33392406986</v>
+        <v>46158.3686215663</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Поплаухина - бухгалтер/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Поплаухина - бухгалтер/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.3686215663</v>
+        <v>46158.37293043792</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
